--- a/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_precious_metals.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,122 +587,116 @@
           <t>Precious Metals</t>
         </is>
       </c>
-      <c r="D2">
-        <v>0.242</v>
-      </c>
-      <c r="E2">
-        <v>0.449</v>
-      </c>
       <c r="G2">
-        <v>0.3198372738733304</v>
+        <v>-0.947565543071161</v>
       </c>
       <c r="H2">
-        <v>0.3198372738733304</v>
+        <v>-0.947565543071161</v>
       </c>
       <c r="I2">
-        <v>0.3309898914901351</v>
+        <v>-1.704119850187266</v>
       </c>
       <c r="J2">
-        <v>0.3161027899238622</v>
+        <v>-1.704119850187266</v>
       </c>
       <c r="K2">
-        <v>61.46</v>
+        <v>-4.85</v>
       </c>
       <c r="L2">
-        <v>0.4753397217259488</v>
+        <v>-1.816479400749064</v>
       </c>
       <c r="M2">
-        <v>4.509</v>
+        <v>5.56</v>
       </c>
       <c r="N2">
-        <v>0.02071103761885076</v>
+        <v>0.06427745664739885</v>
       </c>
       <c r="O2">
-        <v>0.07336479010738692</v>
+        <v>-1.14639175257732</v>
       </c>
       <c r="P2">
-        <v>0.949</v>
+        <v>3.62</v>
       </c>
       <c r="Q2">
-        <v>0.004359009691791833</v>
+        <v>0.04184971098265896</v>
       </c>
       <c r="R2">
-        <v>0.01544093719492353</v>
+        <v>-0.7463917525773197</v>
       </c>
       <c r="S2">
-        <v>3.56</v>
+        <v>1.94</v>
       </c>
       <c r="T2">
-        <v>0.789532047017077</v>
+        <v>0.3489208633093526</v>
       </c>
       <c r="U2">
-        <v>20.62</v>
+        <v>3.798</v>
       </c>
       <c r="V2">
-        <v>0.09471315052133572</v>
+        <v>0.04390751445086705</v>
       </c>
       <c r="W2">
-        <v>0.004576659038901602</v>
+        <v>-0.06718750000000001</v>
       </c>
       <c r="X2">
-        <v>0.1221788136169205</v>
+        <v>0.2276222831972441</v>
       </c>
       <c r="Y2">
-        <v>-0.1176021545780189</v>
+        <v>-0.2948097831972442</v>
       </c>
       <c r="Z2">
-        <v>0.5262521673300935</v>
+        <v>0.03322837977424614</v>
       </c>
       <c r="AA2">
-        <v>-0.05860731059832551</v>
+        <v>-0.05438686505900461</v>
       </c>
       <c r="AB2">
-        <v>0.1221450469663189</v>
+        <v>0.2275725177319056</v>
       </c>
       <c r="AC2">
-        <v>-0.1807523575646444</v>
+        <v>-0.2833283555360269</v>
       </c>
       <c r="AD2">
-        <v>203.806</v>
+        <v>0.882</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>203.806</v>
+        <v>0.882</v>
       </c>
       <c r="AG2">
-        <v>183.186</v>
+        <v>-2.916</v>
       </c>
       <c r="AH2">
-        <v>0.4835071503810057</v>
+        <v>0.01009361195669589</v>
       </c>
       <c r="AI2">
-        <v>0.6023419120689452</v>
+        <v>0.01010517632501547</v>
       </c>
       <c r="AJ2">
-        <v>0.4569414511494253</v>
+        <v>-0.03488705972434916</v>
       </c>
       <c r="AK2">
-        <v>0.5765352368003626</v>
+        <v>-0.03492884864165588</v>
       </c>
       <c r="AL2">
-        <v>0.186</v>
+        <v>0.014</v>
       </c>
       <c r="AM2">
-        <v>-73.02499999999999</v>
+        <v>0.008</v>
       </c>
       <c r="AN2">
-        <v>3.343274278215223</v>
+        <v>-0.625531914893617</v>
       </c>
       <c r="AO2">
-        <v>230.0860215053764</v>
+        <v>-325</v>
       </c>
       <c r="AP2">
-        <v>3.00501968503937</v>
+        <v>2.068085106382979</v>
       </c>
       <c r="AQ2">
-        <v>-0.5860458747004451</v>
+        <v>-568.75</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mangazeya Mining Ltd. (TSXV:MGZ.H)</t>
+          <t>Sailfish Royalty Corp. (TSXV:FISH)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,116 +715,116 @@
           <t>Precious Metals</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.242</v>
-      </c>
-      <c r="E3">
-        <v>0.449</v>
-      </c>
       <c r="G3">
-        <v>0.3478599221789884</v>
+        <v>-0.947565543071161</v>
       </c>
       <c r="H3">
-        <v>0.3478599221789884</v>
+        <v>-0.947565543071161</v>
       </c>
       <c r="I3">
-        <v>0.3688715953307393</v>
+        <v>-0.7453183520599251</v>
       </c>
       <c r="J3">
-        <v>0.2859169636971398</v>
+        <v>-0.7453183520599251</v>
       </c>
       <c r="K3">
-        <v>51.7</v>
+        <v>-1.56</v>
       </c>
       <c r="L3">
-        <v>0.4023346303501946</v>
+        <v>-0.5842696629213483</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>5.56</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.09636048526863085</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>-3.564102564102564</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>3.62</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.06273830155979203</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>-2.320512820512821</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.94</v>
+      </c>
+      <c r="T3">
+        <v>0.3489208633093526</v>
       </c>
       <c r="U3">
-        <v>10.3</v>
+        <v>1.66</v>
       </c>
       <c r="V3">
-        <v>0.1702479338842975</v>
+        <v>0.02876949740034662</v>
       </c>
       <c r="W3">
-        <v>-6.281895504252734</v>
+        <v>-0.03223140495867769</v>
       </c>
       <c r="X3">
-        <v>0.3953873488838182</v>
+        <v>0.2276222831972441</v>
       </c>
       <c r="Y3">
-        <v>-6.677282853136552</v>
+        <v>-0.2598536881559219</v>
       </c>
       <c r="Z3">
-        <v>0.717195959144946</v>
+        <v>0.05980780861501244</v>
       </c>
       <c r="AA3">
-        <v>0.2050584910145808</v>
+        <v>-0.04457585735725646</v>
       </c>
       <c r="AB3">
-        <v>0.1432105527763344</v>
+        <v>0.2275725177319056</v>
       </c>
       <c r="AC3">
-        <v>0.06184793823824641</v>
+        <v>-0.2721483750891621</v>
       </c>
       <c r="AD3">
-        <v>203.4</v>
+        <v>0.023</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>203.4</v>
+        <v>0.023</v>
       </c>
       <c r="AG3">
-        <v>193.1</v>
+        <v>-1.637</v>
       </c>
       <c r="AH3">
-        <v>0.770746494884426</v>
+        <v>0.0003984546887722398</v>
       </c>
       <c r="AI3">
-        <v>0.8336065573770493</v>
+        <v>0.0005421587346486575</v>
       </c>
       <c r="AJ3">
-        <v>0.761435331230284</v>
+        <v>-0.0291992936517846</v>
       </c>
       <c r="AK3">
-        <v>0.826272999572101</v>
+        <v>-0.04015896769128867</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="AM3">
-        <v>-73.2</v>
+        <v>-0.002</v>
       </c>
       <c r="AN3">
-        <v>3.19309262166405</v>
+        <v>-0.01631205673758865</v>
+      </c>
+      <c r="AO3">
+        <v>-497.5</v>
       </c>
       <c r="AP3">
-        <v>3.031397174254317</v>
+        <v>1.160992907801419</v>
       </c>
       <c r="AQ3">
-        <v>-0.6475409836065573</v>
+        <v>995</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Orsu Metals Corporation (TSXV:OSU)</t>
+          <t>Bluebird Merchant Ventures Limited (LSE:BMV)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,7 +844,7 @@
         </is>
       </c>
       <c r="K4">
-        <v>0.02</v>
+        <v>-1.29</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -859,7 +853,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -868,73 +862,73 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.767</v>
+        <v>0.118</v>
       </c>
       <c r="V4">
-        <v>0.08706015891032917</v>
+        <v>0.008368794326241135</v>
       </c>
       <c r="W4">
-        <v>0.004576659038901602</v>
+        <v>-0.06718750000000001</v>
       </c>
       <c r="X4">
-        <v>0.1221300280452923</v>
+        <v>0.2361188099331271</v>
       </c>
       <c r="Y4">
-        <v>-0.1175533690063907</v>
+        <v>-0.3033063099331271</v>
       </c>
       <c r="Z4">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>-0.02146865089046109</v>
+        <v>-0.05438686505900461</v>
       </c>
       <c r="AB4">
-        <v>0.1221300280452923</v>
+        <v>0.2289414904770222</v>
       </c>
       <c r="AC4">
-        <v>-0.1435986789357534</v>
+        <v>-0.2833283555360269</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>0.859</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>0.859</v>
       </c>
       <c r="AG4">
-        <v>-0.767</v>
+        <v>0.741</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.05742362457383515</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.04483532543452164</v>
       </c>
       <c r="AJ4">
-        <v>-0.09536242695511624</v>
+        <v>0.04992925005053568</v>
       </c>
       <c r="AK4">
-        <v>-0.2082541406462123</v>
+        <v>0.03891602331810304</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>-0</v>
-      </c>
-      <c r="AP4">
-        <v>9.5875</v>
+        <v>0.01</v>
+      </c>
+      <c r="AO4">
+        <v>-106</v>
+      </c>
+      <c r="AQ4">
+        <v>-106</v>
       </c>
     </row>
     <row r="5">
@@ -945,7 +939,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sailfish Royalty Corp. (TSXV:FISH)</t>
+          <t>Cora Gold Limited (AIM:CORA)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -953,315 +947,86 @@
           <t>Precious Metals</t>
         </is>
       </c>
-      <c r="G5">
-        <v>-3.488080301129234</v>
-      </c>
-      <c r="H5">
-        <v>-3.488080301129234</v>
-      </c>
-      <c r="I5">
-        <v>-3.601003764115433</v>
-      </c>
-      <c r="J5">
-        <v>-3.601003764115433</v>
-      </c>
       <c r="K5">
-        <v>2.86</v>
-      </c>
-      <c r="L5">
-        <v>3.588456712672522</v>
+        <v>-2</v>
       </c>
       <c r="M5">
-        <v>4.509</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.05106455266138166</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>1.576573426573427</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.949</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.01074745186862967</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.3318181818181818</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>3.56</v>
-      </c>
-      <c r="T5">
-        <v>0.789532047017077</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>3.81</v>
+        <v>2.02</v>
       </c>
       <c r="V5">
-        <v>0.04314835787089468</v>
+        <v>0.1374149659863946</v>
       </c>
       <c r="W5">
-        <v>0.05896907216494845</v>
+        <v>-0.09132420091324202</v>
       </c>
       <c r="X5">
-        <v>0.1221788136169205</v>
+        <v>0.2275663241472757</v>
       </c>
       <c r="Y5">
-        <v>-0.06320974145197206</v>
+        <v>-0.3188905250605177</v>
       </c>
       <c r="Z5">
-        <v>0.01627527057382071</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>-0.05860731059832551</v>
+        <v>-0.09247842170160296</v>
       </c>
       <c r="AB5">
-        <v>0.1221450469663189</v>
+        <v>0.2275663241472757</v>
       </c>
       <c r="AC5">
-        <v>-0.1807523575646444</v>
+        <v>-0.3200447458488787</v>
       </c>
       <c r="AD5">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>-3.757</v>
+        <v>-2.02</v>
       </c>
       <c r="AH5">
-        <v>0.0005998664448292645</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.001093843518461189</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.04443892457092841</v>
+        <v>-0.1593059936908517</v>
       </c>
       <c r="AK5">
-        <v>-0.08415653069910177</v>
+        <v>-0.08530405405405406</v>
       </c>
       <c r="AL5">
-        <v>0.186</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>0.186</v>
-      </c>
-      <c r="AN5">
-        <v>-0.01992481203007519</v>
-      </c>
-      <c r="AO5">
-        <v>-15.43010752688172</v>
-      </c>
-      <c r="AP5">
-        <v>1.412406015037594</v>
-      </c>
-      <c r="AQ5">
-        <v>-15.43010752688172</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>British Virgin Islands</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Cora Gold Limited (AIM:CORA)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Precious Metals</t>
-        </is>
-      </c>
-      <c r="K6">
-        <v>-0.82</v>
-      </c>
-      <c r="M6">
-        <v>-0</v>
-      </c>
-      <c r="N6">
-        <v>-0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>5.68</v>
-      </c>
-      <c r="V6">
-        <v>0.153929539295393</v>
-      </c>
-      <c r="W6">
-        <v>-0.05093167701863353</v>
-      </c>
-      <c r="X6">
-        <v>0.1221300280452923</v>
-      </c>
-      <c r="Y6">
-        <v>-0.1730617050639258</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>-0.08580593424218122</v>
-      </c>
-      <c r="AB6">
-        <v>0.1221300280452923</v>
-      </c>
-      <c r="AC6">
-        <v>-0.2079359622874735</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>-5.68</v>
-      </c>
-      <c r="AH6">
-        <v>0</v>
-      </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <v>-0.1819346572709801</v>
-      </c>
-      <c r="AK6">
-        <v>-0.3501849568434032</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>British Virgin Islands</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Bluebird Merchant Ventures Limited (LSE:BMV)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Precious Metals</t>
-        </is>
-      </c>
-      <c r="K7">
-        <v>7.7</v>
-      </c>
-      <c r="M7">
-        <v>-0</v>
-      </c>
-      <c r="N7">
-        <v>-0</v>
-      </c>
-      <c r="O7">
-        <v>-0</v>
-      </c>
-      <c r="P7">
-        <v>-0</v>
-      </c>
-      <c r="Q7">
-        <v>-0</v>
-      </c>
-      <c r="R7">
-        <v>-0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0.063</v>
-      </c>
-      <c r="V7">
-        <v>0.00271551724137931</v>
-      </c>
-      <c r="W7">
-        <v>7.12962962962963</v>
-      </c>
-      <c r="X7">
-        <v>0.1233667240351221</v>
-      </c>
-      <c r="Y7">
-        <v>7.006262905594507</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>-0.5847715736040608</v>
-      </c>
-      <c r="AB7">
-        <v>0.1225399473127508</v>
-      </c>
-      <c r="AC7">
-        <v>-0.7073115209168117</v>
-      </c>
-      <c r="AD7">
-        <v>0.353</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0.353</v>
-      </c>
-      <c r="AG7">
-        <v>0.29</v>
-      </c>
-      <c r="AH7">
-        <v>0.0149874750562561</v>
-      </c>
-      <c r="AI7">
-        <v>0.01805349562726947</v>
-      </c>
-      <c r="AJ7">
-        <v>0.01234567901234568</v>
-      </c>
-      <c r="AK7">
-        <v>0.01487942534633145</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>-0.011</v>
-      </c>
-      <c r="AQ7">
-        <v>52.36363636363636</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_precious_metals.xlsx
@@ -588,115 +588,115 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.947565543071161</v>
+        <v>-0.8260869565217391</v>
       </c>
       <c r="H2">
-        <v>-0.947565543071161</v>
+        <v>-0.8260869565217391</v>
       </c>
       <c r="I2">
-        <v>-1.704119850187266</v>
+        <v>-1.907826086956522</v>
       </c>
       <c r="J2">
-        <v>-1.704119850187266</v>
+        <v>-1.907826086956522</v>
       </c>
       <c r="K2">
-        <v>-4.85</v>
+        <v>-6.468</v>
       </c>
       <c r="L2">
-        <v>-1.816479400749064</v>
+        <v>-2.812173913043479</v>
       </c>
       <c r="M2">
-        <v>5.56</v>
+        <v>4.391</v>
       </c>
       <c r="N2">
-        <v>0.06427745664739885</v>
+        <v>0.05592918099605145</v>
       </c>
       <c r="O2">
-        <v>-1.14639175257732</v>
+        <v>-0.6788806431663574</v>
       </c>
       <c r="P2">
-        <v>3.62</v>
+        <v>3.57</v>
       </c>
       <c r="Q2">
-        <v>0.04184971098265896</v>
+        <v>0.04547191440580817</v>
       </c>
       <c r="R2">
-        <v>-0.7463917525773197</v>
+        <v>-0.551948051948052</v>
       </c>
       <c r="S2">
-        <v>1.94</v>
+        <v>0.8210000000000002</v>
       </c>
       <c r="T2">
-        <v>0.3489208633093526</v>
+        <v>0.1869733545889319</v>
       </c>
       <c r="U2">
-        <v>3.798</v>
+        <v>20.519</v>
       </c>
       <c r="V2">
-        <v>0.04390751445086705</v>
+        <v>0.261355241370526</v>
       </c>
       <c r="W2">
-        <v>-0.06718750000000001</v>
+        <v>-0.04633879781420765</v>
       </c>
       <c r="X2">
-        <v>0.2276222831972441</v>
+        <v>0.1370107212462103</v>
       </c>
       <c r="Y2">
-        <v>-0.2948097831972442</v>
+        <v>-0.1833495190604179</v>
       </c>
       <c r="Z2">
-        <v>0.03322837977424614</v>
+        <v>0.02755018925782185</v>
       </c>
       <c r="AA2">
-        <v>-0.05438686505900461</v>
+        <v>-0.04612025611461373</v>
       </c>
       <c r="AB2">
-        <v>0.2275725177319056</v>
+        <v>0.1309507148111329</v>
       </c>
       <c r="AC2">
-        <v>-0.2833283555360269</v>
+        <v>-0.1772831699023733</v>
       </c>
       <c r="AD2">
-        <v>0.882</v>
+        <v>20.813</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.882</v>
+        <v>20.813</v>
       </c>
       <c r="AG2">
-        <v>-2.916</v>
+        <v>0.2940000000000005</v>
       </c>
       <c r="AH2">
-        <v>0.01009361195669589</v>
+        <v>0.2095486443220603</v>
       </c>
       <c r="AI2">
-        <v>0.01010517632501547</v>
+        <v>0.202042460660305</v>
       </c>
       <c r="AJ2">
-        <v>-0.03488705972434916</v>
+        <v>0.003730775087559013</v>
       </c>
       <c r="AK2">
-        <v>-0.03492884864165588</v>
+        <v>0.003563895556040445</v>
       </c>
       <c r="AL2">
-        <v>0.014</v>
+        <v>0.892</v>
       </c>
       <c r="AM2">
-        <v>0.008</v>
+        <v>0.5960000000000001</v>
       </c>
       <c r="AN2">
-        <v>-0.625531914893617</v>
+        <v>-11.89994282447113</v>
       </c>
       <c r="AO2">
-        <v>-325</v>
+        <v>-4.919282511210763</v>
       </c>
       <c r="AP2">
-        <v>2.068085106382979</v>
+        <v>-0.168096054888508</v>
       </c>
       <c r="AQ2">
-        <v>-568.75</v>
+        <v>-7.362416107382549</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sailfish Royalty Corp. (TSXV:FISH)</t>
+          <t>Bluebird Merchant Ventures Limited (LSE:BMV)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,116 +715,92 @@
           <t>Precious Metals</t>
         </is>
       </c>
-      <c r="G3">
-        <v>-0.947565543071161</v>
-      </c>
-      <c r="H3">
-        <v>-0.947565543071161</v>
-      </c>
-      <c r="I3">
-        <v>-0.7453183520599251</v>
-      </c>
-      <c r="J3">
-        <v>-0.7453183520599251</v>
-      </c>
       <c r="K3">
-        <v>-1.56</v>
-      </c>
-      <c r="L3">
-        <v>-0.5842696629213483</v>
+        <v>-0.848</v>
       </c>
       <c r="M3">
-        <v>5.56</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.09636048526863085</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-3.564102564102564</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>3.62</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.06273830155979203</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-2.320512820512821</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>1.94</v>
-      </c>
-      <c r="T3">
-        <v>0.3489208633093526</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1.66</v>
+        <v>0.519</v>
       </c>
       <c r="V3">
-        <v>0.02876949740034662</v>
+        <v>0.1204176334106729</v>
       </c>
       <c r="W3">
-        <v>-0.03223140495867769</v>
+        <v>-0.04633879781420765</v>
       </c>
       <c r="X3">
-        <v>0.2276222831972441</v>
+        <v>0.1370107212462103</v>
       </c>
       <c r="Y3">
-        <v>-0.2598536881559219</v>
+        <v>-0.1833495190604179</v>
       </c>
       <c r="Z3">
-        <v>0.05980780861501244</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.04457585735725646</v>
+        <v>-0.04506065857885615</v>
       </c>
       <c r="AB3">
-        <v>0.2275725177319056</v>
+        <v>0.1309507148111329</v>
       </c>
       <c r="AC3">
-        <v>-0.2721483750891621</v>
+        <v>-0.1760113733899891</v>
       </c>
       <c r="AD3">
-        <v>0.023</v>
+        <v>0.353</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.023</v>
+        <v>0.353</v>
       </c>
       <c r="AG3">
-        <v>-1.637</v>
+        <v>-0.166</v>
       </c>
       <c r="AH3">
-        <v>0.0003984546887722398</v>
+        <v>0.07570233755093288</v>
       </c>
       <c r="AI3">
-        <v>0.0005421587346486575</v>
+        <v>0.01769157520172405</v>
       </c>
       <c r="AJ3">
-        <v>-0.0291992936517846</v>
+        <v>-0.04005791505791508</v>
       </c>
       <c r="AK3">
-        <v>-0.04015896769128867</v>
+        <v>-0.008541730986930124</v>
       </c>
       <c r="AL3">
-        <v>0.004</v>
+        <v>0.251</v>
       </c>
       <c r="AM3">
-        <v>-0.002</v>
-      </c>
-      <c r="AN3">
-        <v>-0.01631205673758865</v>
+        <v>0.251</v>
       </c>
       <c r="AO3">
-        <v>-497.5</v>
-      </c>
-      <c r="AP3">
-        <v>1.160992907801419</v>
+        <v>-3.418326693227092</v>
       </c>
       <c r="AQ3">
-        <v>995</v>
+        <v>-3.418326693227092</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +811,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bluebird Merchant Ventures Limited (LSE:BMV)</t>
+          <t>Sailfish Royalty Corp. (TSXV:FISH)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -843,92 +819,116 @@
           <t>Precious Metals</t>
         </is>
       </c>
+      <c r="G4">
+        <v>-0.391304347826087</v>
+      </c>
+      <c r="H4">
+        <v>-0.391304347826087</v>
+      </c>
+      <c r="I4">
+        <v>-0.8173913043478261</v>
+      </c>
+      <c r="J4">
+        <v>-0.8173913043478261</v>
+      </c>
       <c r="K4">
-        <v>-1.29</v>
+        <v>-1.45</v>
+      </c>
+      <c r="L4">
+        <v>-0.6304347826086957</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>4.391</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.06904088050314465</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-3.028275862068966</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>3.57</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.05613207547169811</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-2.462068965517241</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.8210000000000002</v>
+      </c>
+      <c r="T4">
+        <v>0.1869733545889319</v>
       </c>
       <c r="U4">
-        <v>0.118</v>
+        <v>1.5</v>
       </c>
       <c r="V4">
-        <v>0.008368794326241135</v>
+        <v>0.02358490566037736</v>
       </c>
       <c r="W4">
-        <v>-0.06718750000000001</v>
+        <v>-0.03419811320754717</v>
       </c>
       <c r="X4">
-        <v>0.2361188099331271</v>
+        <v>0.135899749354161</v>
       </c>
       <c r="Y4">
-        <v>-0.3033063099331271</v>
+        <v>-0.1700978625617082</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>0.05642371758702744</v>
       </c>
       <c r="AA4">
-        <v>-0.05438686505900461</v>
+        <v>-0.04612025611461373</v>
       </c>
       <c r="AB4">
-        <v>0.2289414904770222</v>
+        <v>0.1311629137877596</v>
       </c>
       <c r="AC4">
-        <v>-0.2833283555360269</v>
+        <v>-0.1772831699023733</v>
       </c>
       <c r="AD4">
-        <v>0.859</v>
+        <v>4.06</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.859</v>
+        <v>4.06</v>
       </c>
       <c r="AG4">
-        <v>0.741</v>
+        <v>2.56</v>
       </c>
       <c r="AH4">
-        <v>0.05742362457383515</v>
+        <v>0.06000591191250369</v>
       </c>
       <c r="AI4">
-        <v>0.04483532543452164</v>
+        <v>0.09745559289486316</v>
       </c>
       <c r="AJ4">
-        <v>0.04992925005053568</v>
+        <v>0.03869407496977025</v>
       </c>
       <c r="AK4">
-        <v>0.03891602331810304</v>
+        <v>0.06374501992031871</v>
       </c>
       <c r="AL4">
-        <v>0.01</v>
+        <v>0.156</v>
       </c>
       <c r="AM4">
-        <v>0.01</v>
+        <v>0.103</v>
+      </c>
+      <c r="AN4">
+        <v>-2.942028985507246</v>
       </c>
       <c r="AO4">
-        <v>-106</v>
+        <v>-12.05128205128205</v>
+      </c>
+      <c r="AP4">
+        <v>-1.855072463768116</v>
       </c>
       <c r="AQ4">
-        <v>-106</v>
+        <v>-18.25242718446602</v>
       </c>
     </row>
     <row r="5">
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="K5">
-        <v>-2</v>
+        <v>-4.17</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -972,61 +972,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>2.02</v>
+        <v>18.5</v>
       </c>
       <c r="V5">
-        <v>0.1374149659863946</v>
+        <v>1.745283018867925</v>
       </c>
       <c r="W5">
-        <v>-0.09132420091324202</v>
+        <v>-0.1622568093385214</v>
       </c>
       <c r="X5">
-        <v>0.2275663241472757</v>
+        <v>0.2271172225086041</v>
       </c>
       <c r="Y5">
-        <v>-0.3188905250605177</v>
+        <v>-0.3893740318471255</v>
       </c>
       <c r="Z5">
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>-0.09247842170160296</v>
+        <v>-0.06967905405405406</v>
       </c>
       <c r="AB5">
-        <v>0.2275663241472757</v>
+        <v>0.1203626892328505</v>
       </c>
       <c r="AC5">
-        <v>-0.3200447458488787</v>
+        <v>-0.1900417432869045</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>16.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>16.4</v>
       </c>
       <c r="AG5">
-        <v>-2.02</v>
+        <v>-2.100000000000001</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.6074074074074074</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.3961352657004831</v>
       </c>
       <c r="AJ5">
-        <v>-0.1593059936908517</v>
+        <v>-0.247058823529412</v>
       </c>
       <c r="AK5">
-        <v>-0.08530405405405406</v>
+        <v>-0.09170305676855901</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.485</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>0.242</v>
+      </c>
+      <c r="AN5">
+        <v>-44.44444444444444</v>
+      </c>
+      <c r="AO5">
+        <v>-3.402061855670103</v>
+      </c>
+      <c r="AP5">
+        <v>5.69105691056911</v>
+      </c>
+      <c r="AQ5">
+        <v>-6.818181818181818</v>
       </c>
     </row>
   </sheetData>
